--- a/src/main/resources/python/MultifacetedModeling/Results/OnAllTrainKernel/DKNCOR/Know+Pos-Kernel/mlr.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnAllTrainKernel/DKNCOR/Know+Pos-Kernel/mlr.xlsx
@@ -39,25 +39,25 @@
     <t>Time</t>
   </si>
   <si>
-    <t>[2, 3, 4, 8, 9, 12, 14, 16, 19, 21, 29, 31, 33, 34, 35, 36, 37, 38, 40, 41, 42]</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>0.3894</t>
-  </si>
-  <si>
-    <t>0.0386</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>0.8157</t>
-  </si>
-  <si>
-    <t>0.626</t>
+    <t>[1, 2, 3, 4, 6, 8, 9, 10, 13, 14, 29, 30, 32, 34, 35, 36, 37, 39, 40]</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>0.219</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>0.1368</t>
+  </si>
+  <si>
+    <t>0.7221</t>
+  </si>
+  <si>
+    <t>0.5865</t>
   </si>
 </sst>
 </file>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[2, 3, 8, 9, 10, 11, 13, 14, 16, 20, 21, 22, 24, 29, 31, 35, 37, 38, 41]</t>
+          <t>[0, 2, 3, 4, 8, 9, 10, 12, 14, 20, 27, 28, 30, 31, 34, 35, 37, 42, 43]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -527,175 +527,175 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.3515151515151515</t>
+          <t>0.4380952380952381</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.035815419023903776</t>
+          <t>0.037521774747561326</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.08173437522942731</t>
+          <t>0.13815661667947862</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.8333195728616835</t>
+          <t>0.716526868576648</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.6024575233459473</t>
+          <t>0.5868029594421387</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 5, 8, 9, 12, 14, 15, 16, 19, 20, 22, 27, 28, 29, 30, 32, 35, 36, 37, 39, 43]</t>
+          <t>[1, 2, 3, 4, 6, 7, 8, 9, 12, 14, 15, 17, 20, 23, 24, 26, 28, 29, 31, 32, 34, 35, 36, 37, 39, 41]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7954545454545454</t>
+          <t>0.7642857142857142</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.039749657041749833</t>
+          <t>0.03703302086693857</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.10128547906161195</t>
+          <t>0.2135276175380403</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7440415430621556</t>
+          <t>0.3228628652341379</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6316916942596436</t>
+          <t>0.607271671295166</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 8, 9, 12, 14, 16, 19, 21, 29, 31, 33, 34, 35, 36, 37, 38, 40, 41, 42]</t>
+          <t>[1, 2, 3, 4, 6, 8, 9, 10, 13, 14, 29, 30, 32, 34, 35, 36, 37, 39, 40]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.38939393939393935</t>
+          <t>0.21904761904761905</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.038641995861713394</t>
+          <t>0.037978252113022956</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.08595280009975029</t>
+          <t>0.13678377545582154</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.8156703625566908</t>
+          <t>0.7221325366982118</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.6259536743164062</t>
+          <t>0.5865490436553955</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 8, 9, 10, 11, 12, 14, 15, 16, 17, 18, 19, 23, 29, 37, 38, 39, 43, 44]</t>
+          <t>[0, 2, 8, 9, 11, 14, 15, 20, 27, 29, 34, 35, 36, 37, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.3363636363636363</t>
+          <t>0.12380952380952381</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.039322075223036095</t>
+          <t>0.03503727982394976</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.16644920296905003</t>
+          <t>0.19595374826397044</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.30874457926444876</t>
+          <t>0.4297363714116378</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6263964176177979</t>
+          <t>0.5966572761535645</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 8, 9, 10, 12, 14, 15, 16, 18, 19, 21, 23, 26, 29, 31, 32, 33, 35, 37, 38, 40, 43]</t>
+          <t>[0, 2, 8, 9, 10, 13, 14, 17, 18, 19, 21, 23, 26, 28, 30, 31, 34, 35, 37, 42]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.2909090909090909</t>
+          <t>0.2833333333333333</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.03635305893821668</t>
+          <t>0.035734989566486255</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.09067731768826819</t>
+          <t>0.15259135028386075</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.7948495660838375</t>
+          <t>0.6541973198320616</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.6110165119171143</t>
+          <t>0.5785465240478516</t>
         </is>
       </c>
     </row>
